--- a/02_加值成品/九上/九上7-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-2 月球與月相　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上7-2 月球與月相　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>月球本身會發光嗎？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>初七八</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>新月</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>月球靠什麼而亮？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>反射陽光</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>新月</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>初七八</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>月球繞什麼公轉？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>地球</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>滿月</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>衛星</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>月相變化是什麼改變造成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>月相日常變化、月食特殊遮蔽</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>日地月相對位置</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>地球在日月之間,面向地球的月面全被照亮</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>月相週期約幾天？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>月相日常變化、月食特殊遮蔽</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>29.5天</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>約一個月</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>農曆初一大約是什麼月相？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>朔望月</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>初七八</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>滿月</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>新月</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>看不見</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>農曆十五大約是什麼月相？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>新月</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>滿月</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>太陽光</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>最圓</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>滿月之後接近哪個月相？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>新月</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>下弦月</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>漸缺</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>月球繞什麼天體公轉？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>地球</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>衛星</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>我們看到月亮是因它反射？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>新月</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>下弦月</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>太陽光</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-2 月球與月相　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上7-2 月球與月相　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>月相順序為？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>月食發生在滿月但需三者精確成線</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>地球影子(那是月食)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>日-地-月成一線</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>新月上弦滿月下弦</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>循環</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>月相是地球影子造成的嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>初七八</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>相對位置</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>月相與月食差別？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>月相日常變化、月食特殊遮蔽</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>新月上弦滿月下弦</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>日-月-地(月在中)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>滿月時三者排列？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>日-月-地(月在中)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>日-地-月成一線</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>日地月相對位置</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>月球在日地之間被照亮面背向地球</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>地在中</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>新月時三者排列？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>地球影子(那是月食)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>新月上弦滿月下弦</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>較複雜移至進階,國中重成因</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>日-月-地(月在中)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>同側</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>月球不發光卻明亮因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>反射太陽光</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>初七八</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>上弦月大約出現在農曆？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>下弦月</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>初七八</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>半圓</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>月相變化週期又稱？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>朔望月</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>下弦月</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>反射太陽光</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>約29.5天</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>農曆十五通常看到什麼月相？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>新月</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>滿月</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>最圓</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>月相盈虧一個週期約？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>下弦月</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>日-月-地(月在中)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>29.5天</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>朔望月</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上7-2 月球與月相　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上7-2 月球與月相　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>用日地月位置說明滿月成因？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>地球在日月之間,面向地球的月面全被照亮</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>日-地-月成一線</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>月球繞地公轉造成相位變化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>新月上弦滿月下弦</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>位置</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何月相不是地球影子造成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>月相日常變化、月食特殊遮蔽</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>是相對位置改變照亮部分,影子造成的是月食</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>月球在日地之間被照亮面背向地球</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>月球繞地公轉造成相位變化</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>新月為何幾乎看不見？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>月球在日地之間被照亮面背向地球</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>日-月-地(月在中)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>月球繞地公轉造成相位變化</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>新月上弦滿月下弦</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>位置</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>月相從新月到滿月約需幾天？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>約15天</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>地球影子(那是月食)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>朔望月</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>半週期</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>中秋為何看到滿月？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>農曆十五地球在日月間</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>日-地-月成一線</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>月球繞地公轉造成相位變化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>新月上弦滿月下弦</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>望</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>月食與滿月的關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>新月上弦滿月下弦</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>日地月相對位置</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>月食發生在滿月但需三者精確成線</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>觀察連續數晚月相可推知？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>日地月相對位置</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>月相日常變化、月食特殊遮蔽</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>月球繞地公轉造成相位變化</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>運動</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱不涉月亮升落方位？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>日-月-地(月在中)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>較複雜移至進階,國中重成因</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>日地月相對位置</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>農曆十五地球在日月間</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>新月時幾乎看不到月亮的原因？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>被照亮面背向地球</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>月球在日地之間被照亮面背向地球</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>日-地-月成一線</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>位置</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>月相變化是相對位置而非什麼造成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>地球影子(那是月食)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>地球在日月之間,面向地球的月面全被照亮</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>月相日常變化、月食特殊遮蔽</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>月球繞地公轉造成相位變化</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上7-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：月球本身不會發光，我們看到的月光其實是月球表面反射太陽光的緣故</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：月球表面反射太陽的光線，這些反射光傳到地球，我們才看得見明亮的月亮</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>衛星</t>
+          <t>衛星：月球是地球的天然衛星，會固定繞著地球公轉</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>位置：太陽、地球、月球三者的相對位置隨月球公轉不斷改變，使我們看到月球被照亮的部分比例不同，形成月相變化</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>約一個月</t>
+          <t>約一個月：月相從新月變化回新月的完整週期大約是29.5天，接近一個月的長度</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>看不見</t>
+          <t>看不見：農曆初一時月球運行到太陽和地球之間，被照亮的一面背向地球，幾乎看不到月亮，這就是新月</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>最圓</t>
+          <t>最圓：農曆十五前後，地球運行到太陽和月亮之間，月球被照亮的一面完全朝向地球，所以看到滿月</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>漸缺</t>
+          <t>漸缺：滿月之後，月球持續公轉，被照亮的部分逐漸減少，會依序經過下弦月再回到新月</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>衛星</t>
+          <t>衛星：月球是地球的天然衛星,會固定繞著地球公轉</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：月球本身不會發光,我們看到的月光其實是月球表面反射太陽光的緣故</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>循環</t>
+          <t>循環：月相依序循環變化，從新月開始逐漸變亮到上弦月，再到滿月，之後逐漸變暗經過下弦月，最後回到新月</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>相對位置</t>
+          <t>相對位置：月相變化是因為太陽、地球、月球三者的相對位置改變，造成月球被照亮部分的角度不同，並不是地球的影子擋住月球造成的(那是月食)</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：月相是每個月都會規律出現、因相對位置改變造成的日常現象；月食則是三者精確排成一直線、地球影子遮住月球的特殊少見現象，兩者成因不同</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>地在中</t>
+          <t>地在中：滿月時地球剛好位在太陽和月球之間，三者大致排成一直線，月球被照亮的一面完全朝向地球</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>同側</t>
+          <t>同側：新月時月球剛好位在太陽和地球之間，三者大致排成一直線，月球被照亮的一面背向地球</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：月球本身不會發光，我們看到的明亮月光其實是月球表面反射太陽光造成的</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>半圓</t>
+          <t>半圓：月相從新月逐漸變亮到半圓形狀的上弦月，大約出現在農曆初七、八左右</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>約29.5天</t>
+          <t>約29.5天：月相從新月(朔)到下次新月的完整週期稱為朔望月，長度約29.5天</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>最圓</t>
+          <t>最圓：農曆十五前後,地球運行到太陽和月亮之間,月球被照亮的一面完全朝向地球,所以看到滿月</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>朔望月</t>
+          <t>朔望月：月球繞地球一圈、月相從新月變化回新月的週期大約是29.5天,稱為一個朔望月</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>位置：滿月時地球運行到太陽和月球之間，太陽光從地球後方照向月球，使月球面向地球的整面都被照亮，因此我們看到又大又圓的滿月</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：月相盈虧的成因是太陽、地球、月球三者相對位置改變，使我們能看到月球被照亮部分的角度不同；地球影子真正遮住月球、造成月球變暗的現象是月食，兩者是完全不同的機制，不要混淆</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>位置：新月時月球位在地球和太陽之間，被太陽照亮的那一面正好背對地球，朝向地球的是沒被照到的暗面，所以幾乎看不到月亮</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>半週期</t>
+          <t>半週期：完整的月相週期(朔望月)約29.5天，從新月變化到滿月大約經過一半的週期，也就是約15天左右</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>望</t>
+          <t>望：農曆十五左右地球運行到太陽和月亮之間，月亮被太陽整面照亮，從地球看就是滿月</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>條件：月食一定發生在滿月的時候(地球位在日月之間)，但並非每次滿月都會發生月食，還需要太陽、地球、月球三者精確排成一直線，地球影子才能真正遮住月球</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>運動</t>
+          <t>運動：連續觀察好幾個晚上會發現月亮的形狀逐漸改變，這正反映了月球持續繞地球公轉、與太陽的相對位置不斷變化，造成月相隨之改變</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：月亮在天空中升起與落下的確切方位牽涉較複雜的天球座標概念，依課綱安排移到更進階的階段學習，國中階段的重點放在理解月相變化的成因即可</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>位置：新月時月球位在地球和太陽之間,被太陽照亮的那一面正好背對地球,朝向地球的是沒被照到的暗面,所以幾乎看不到月亮</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：月相盈虧是因為太陽、地球、月球三者的相對位置改變,造成月球被照亮部分的角度不同;這和地球擋住陽光造成月食是完全不同的現象,不要搞混</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上7-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上7-2_三種難度測驗卷.xlsx
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>反射陽光</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>反射太陽光</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>月相日常變化、月食特殊遮蔽</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>反射陽光</t>
+          <t>太陽光</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>新月</t>
+          <t>下弦月</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>下弦月</t>
+          <t>滿月</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>下弦月</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>反射陽光</t>
+          <t>新月</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>初七八</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>日-月-地(月在中)</t>
+          <t>約15天</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>反射太陽光</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>日-月-地(月在中)</t>
+          <t>較複雜移至進階,國中重成因</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>月球繞地公轉造成相位變化</t>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>新月上弦滿月下弦</t>
+          <t>月相日常變化、月食特殊遮蔽</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1640,17 +1640,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>地球影子(那是月食)</t>
+          <t>下弦月</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>朔望月</t>
+          <t>反射陽光</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>反射太陽光</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>月球在日地之間被照亮面背向地球</t>
+          <t>日地月相對位置</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>日-地-月成一線</t>
+          <t>是相對位置改變照亮部分,影子造成的是月食</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>是相對位置改變照亮部分,影子造成的是月食</t>
+          <t>月相日常變化、月食特殊遮蔽</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
